--- a/Basico/21 - Funções de Contagem 1.xlsx
+++ b/Basico/21 - Funções de Contagem 1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wilck.alunos\Desktop\Luiz Henrique Vidal Araujo - Excel completo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wilck.alunos\Desktop\EXCEL-completo\Basico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F77AFD73-00F6-4631-8E55-9C0B533D8332}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54FE5797-47D3-4F67-86B4-A4770731CBB8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15360" windowHeight="7425" firstSheet="15" activeTab="16" xr2:uid="{A5E3398E-808E-49BA-92C6-AB43937C9D3D}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15360" windowHeight="7425" firstSheet="15" activeTab="20" xr2:uid="{A5E3398E-808E-49BA-92C6-AB43937C9D3D}"/>
   </bookViews>
   <sheets>
     <sheet name="01-formatacao" sheetId="1" r:id="rId1"/>
